--- a/data/trans_camb/P16A13-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A13-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 7,89</t>
+          <t>0,2; 8,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,04</t>
+          <t>-2,41; 2,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 9,95</t>
+          <t>0,43; 10,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 7,5</t>
+          <t>0,54; 7,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 9,1</t>
+          <t>1,61; 9,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 4,57</t>
+          <t>-1,15; 4,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,51</t>
+          <t>1,35; 6,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,19</t>
+          <t>0,67; 5,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,27</t>
+          <t>0,57; 5,87</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 664,17</t>
+          <t>-11,41; 615,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-61,94; 269,77</t>
+          <t>-64,9; 209,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 684,53</t>
+          <t>-11,39; 732,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 531,13</t>
+          <t>-2,24; 456,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,48; 630,13</t>
+          <t>25,99; 648,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 333,06</t>
+          <t>-29,37; 324,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,46; 341,08</t>
+          <t>28,26; 365,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 266,82</t>
+          <t>12,58; 315,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,0; 335,17</t>
+          <t>2,6; 290,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 4,6</t>
+          <t>-0,69; 4,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,89</t>
+          <t>-3,32; 0,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 1,46</t>
+          <t>-3,18; 1,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 5,22</t>
+          <t>-0,49; 5,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,14</t>
+          <t>-4,34; -0,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,58</t>
+          <t>-2,59; 1,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,96</t>
+          <t>0,34; 4,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; -0,3</t>
+          <t>-3,13; -0,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,86</t>
+          <t>-2,16; 1,01</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,83; 190,55</t>
+          <t>-18,38; 188,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,23; 50,61</t>
+          <t>-71,52; 45,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-69,92; 71,45</t>
+          <t>-69,47; 67,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 204,3</t>
+          <t>-10,31; 190,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,04; 2,93</t>
+          <t>-81,87; 3,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 64,79</t>
+          <t>-52,28; 69,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 137,63</t>
+          <t>6,21; 145,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-71,8; -8,8</t>
+          <t>-70,92; -5,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,84; 33,39</t>
+          <t>-48,46; 36,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,31</t>
+          <t>-0,0; 5,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,44</t>
+          <t>-1,57; 2,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,83; 12,58</t>
+          <t>5,84; 12,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,23</t>
+          <t>-2,64; 3,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,46</t>
+          <t>-4,26; 0,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,55; 15,63</t>
+          <t>8,54; 15,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,28</t>
+          <t>-0,68; 3,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,88</t>
+          <t>-2,3; 0,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,56; 13,32</t>
+          <t>8,28; 13,34</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 1177,51</t>
+          <t>-15,84; 1127,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-70,85; 431,89</t>
+          <t>-77,49; 408,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>178,66; 2044,69</t>
+          <t>165,04; 1841,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,82; 145,52</t>
+          <t>-50,7; 174,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-85,56; 34,84</t>
+          <t>-82,07; 73,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>152,87; 733,05</t>
+          <t>148,06; 715,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,06; 167,73</t>
+          <t>-23,72; 174,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-67,33; 57,65</t>
+          <t>-66,45; 49,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>230,83; 812,72</t>
+          <t>212,86; 770,91</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,62</t>
+          <t>-2,03; 2,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 5,09</t>
+          <t>-0,28; 5,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 7,56</t>
+          <t>1,31; 7,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 7,17</t>
+          <t>0,35; 7,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 7,37</t>
+          <t>0,25; 7,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 6,9</t>
+          <t>-0,41; 7,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,11</t>
+          <t>-0,12; 4,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,25</t>
+          <t>0,84; 5,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,21</t>
+          <t>1,41; 6,42</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,67; 298,81</t>
+          <t>-71,41; 308,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 484,34</t>
+          <t>-24,39; 538,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,58; 725,96</t>
+          <t>22,35; 742,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,59; 244,9</t>
+          <t>3,61; 260,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 251,79</t>
+          <t>-0,32; 262,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,03; 241,33</t>
+          <t>-6,73; 240,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 181,4</t>
+          <t>-5,46; 172,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,03; 226,13</t>
+          <t>19,81; 245,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>40,08; 270,72</t>
+          <t>34,42; 271,05</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,64; 10,94</t>
+          <t>2,16; 10,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 2,01</t>
+          <t>-2,65; 2,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,52; 15,52</t>
+          <t>7,31; 16,13</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 7,56</t>
+          <t>-1,02; 7,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,8</t>
+          <t>-4,64; 2,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,7; 21,61</t>
+          <t>12,27; 21,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,96</t>
+          <t>1,84; 8,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,65</t>
+          <t>-2,69; 1,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,48; 17,84</t>
+          <t>11,55; 17,97</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>39,73; 1611,24</t>
+          <t>30,28; 1655,47</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1657,37 +1657,37 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>179,85; 2835,03</t>
+          <t>177,34; 2768,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 335,21</t>
+          <t>-26,43; 371,23</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 156,24</t>
+          <t>-77,17; 135,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>174,05; 1083,54</t>
+          <t>157,17; 1042,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,76; 430,21</t>
+          <t>36,03; 454,74</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-66,94; 101,11</t>
+          <t>-65,89; 113,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>237,83; 937,84</t>
+          <t>233,6; 1018,78</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,47; 7,13</t>
+          <t>0,39; 6,84</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,23</t>
+          <t>-1,26; 3,78</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8,53; 15,53</t>
+          <t>8,56; 15,81</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 2,84</t>
+          <t>-3,48; 2,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 1,39</t>
+          <t>-5,07; 1,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,66; 15,39</t>
+          <t>7,65; 15,86</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,92</t>
+          <t>-0,82; 3,85</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,85</t>
+          <t>-2,35; 1,6</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,2; 14,6</t>
+          <t>9,21; 14,53</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 1042,57</t>
+          <t>-6,86; 942,89</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-46,53; 631,2</t>
+          <t>-47,94; 577,23</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>219,27; 1991,73</t>
+          <t>224,05; 1963,64</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-60,61; 132,87</t>
+          <t>-60,65; 113,74</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-81,71; 81,93</t>
+          <t>-84,07; 56,95</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>114,4; 663,23</t>
+          <t>104,0; 629,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 211,72</t>
+          <t>-23,55; 178,7</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-53,48; 103,77</t>
+          <t>-57,0; 74,2</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>193,73; 757,86</t>
+          <t>206,34; 737,44</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,5</t>
+          <t>-1,6; 2,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,81</t>
+          <t>-1,36; 3,21</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,7</t>
+          <t>0,24; 4,91</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,22</t>
+          <t>-1,79; 3,05</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,93</t>
+          <t>-2,18; 2,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 4,7</t>
+          <t>-2,59; 4,88</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,23</t>
+          <t>-1,12; 2,04</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,17</t>
+          <t>-1,06; 2,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 4,07</t>
+          <t>-0,38; 4,15</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-47,13; 119,6</t>
+          <t>-39,1; 135,79</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-37,45; 132,93</t>
+          <t>-35,79; 163,39</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1,72; 208,91</t>
+          <t>1,43; 223,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-30,22; 93,31</t>
+          <t>-32,14; 94,32</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-35,56; 87,26</t>
+          <t>-37,99; 77,18</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 116,3</t>
+          <t>-42,13; 127,54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 69,95</t>
+          <t>-24,69; 66,52</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 67,63</t>
+          <t>-23,97; 69,01</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 121,71</t>
+          <t>-5,42; 126,04</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,45</t>
+          <t>-2,13; 1,44</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,33</t>
+          <t>-2,09; 1,57</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,47</t>
+          <t>-2,72; 1,56</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>-0,0; 3,59</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,73</t>
+          <t>-0,71; 2,65</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,3</t>
+          <t>-0,95; 2,14</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,06</t>
+          <t>-0,52; 2,11</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,46</t>
+          <t>-0,83; 1,72</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,38</t>
+          <t>-1,1; 1,47</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 68,62</t>
+          <t>-56,69; 69,13</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-56,17; 66,85</t>
+          <t>-52,78; 75,81</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 63,89</t>
+          <t>-68,62; 63,44</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 243,4</t>
+          <t>-5,74; 250,42</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 177,96</t>
+          <t>-26,97; 171,59</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 165,86</t>
+          <t>-30,26; 144,96</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 95,53</t>
+          <t>-17,9; 110,2</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 71,41</t>
+          <t>-26,72; 79,12</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 62,09</t>
+          <t>-34,94; 67,62</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,47</t>
+          <t>0,49; 2,4</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,15</t>
+          <t>-0,51; 1,15</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,48</t>
+          <t>1,83; 4,4</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,78</t>
+          <t>0,69; 2,79</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,39</t>
+          <t>-0,44; 1,48</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,28</t>
+          <t>2,74; 5,29</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,27</t>
+          <t>1,01; 2,36</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,05</t>
+          <t>-0,21; 0,99</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,64</t>
+          <t>2,81; 4,59</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>21,4; 109,54</t>
+          <t>14,96; 110,7</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 47,88</t>
+          <t>-17,3; 52,04</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>69,24; 203,3</t>
+          <t>61,79; 199,35</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>17,56; 86,16</t>
+          <t>17,18; 89,73</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 43,52</t>
+          <t>-11,1; 47,18</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>69,34; 164,69</t>
+          <t>73,61; 169,91</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>29,56; 81,8</t>
+          <t>28,91; 83,67</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 37,34</t>
+          <t>-6,53; 34,88</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>87,23; 167,78</t>
+          <t>84,02; 158,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A13-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A13-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,7</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,06</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 8,08</t>
+          <t>0,06; 7,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,82</t>
+          <t>-2,31; 3,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 10,61</t>
+          <t>-0,63; 6,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 7,62</t>
+          <t>0,53; 7,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,75</t>
+          <t>1,73; 9,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,28</t>
+          <t>-1,68; 3,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,36</t>
+          <t>1,2; 6,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,4</t>
+          <t>0,54; 5,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,87</t>
+          <t>-0,06; 4,14</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143,33%</t>
+          <t>100,83%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>103,95%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 615,79</t>
+          <t>-10,85; 497,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,9; 209,67</t>
+          <t>-62,53; 286,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 732,06</t>
+          <t>-20,81; 446,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 456,86</t>
+          <t>-8,11; 510,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,99; 648,68</t>
+          <t>25,53; 611,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,37; 324,3</t>
+          <t>-39,66; 271,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,26; 365,69</t>
+          <t>27,0; 361,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,58; 315,2</t>
+          <t>9,36; 288,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 290,01</t>
+          <t>-4,49; 235,94</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,64</t>
+          <t>-0,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,48</t>
+          <t>-0,73; 4,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,83</t>
+          <t>-3,52; 0,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 1,45</t>
+          <t>-3,35; 1,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 5,02</t>
+          <t>-0,44; 4,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,34; -0,24</t>
+          <t>-4,28; -0,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,77</t>
+          <t>-2,77; 1,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,13</t>
+          <t>0,27; 4,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; -0,28</t>
+          <t>-3,19; -0,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,01</t>
+          <t>-2,29; 0,69</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-25,33%</t>
+          <t>-26,82%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-10,47%</t>
+          <t>-13,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-17,67%</t>
+          <t>-19,86%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 188,78</t>
+          <t>-17,59; 197,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,52; 45,04</t>
+          <t>-73,32; 50,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-69,47; 67,57</t>
+          <t>-68,15; 60,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,31; 190,4</t>
+          <t>-8,98; 209,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-81,87; 3,55</t>
+          <t>-83,13; -1,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,28; 69,5</t>
+          <t>-53,43; 59,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 145,69</t>
+          <t>5,23; 155,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,92; -5,41</t>
+          <t>-70,64; -3,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 36,33</t>
+          <t>-50,7; 26,34</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,02</t>
+          <t>9,23</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,35</t>
+          <t>12,72</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>11,12</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,49</t>
+          <t>-0,33; 5,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,34</t>
+          <t>-1,51; 2,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 12,32</t>
+          <t>6,02; 13,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,42</t>
+          <t>-2,57; 3,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 0,91</t>
+          <t>-4,5; 0,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,91</t>
+          <t>9,11; 16,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,32</t>
+          <t>-0,52; 3,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,88</t>
+          <t>-2,21; 1,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 13,34</t>
+          <t>8,73; 13,51</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>587,21%</t>
+          <t>601,12%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>335,65%</t>
+          <t>345,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>409,64%</t>
+          <t>422,03%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 1127,68</t>
+          <t>-40,64; 799,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,49; 408,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>165,04; 1841,72</t>
+          <t>208,58; 2032,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 174,67</t>
+          <t>-54,83; 134,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-82,07; 73,67</t>
+          <t>-84,4; 53,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>148,06; 715,19</t>
+          <t>162,51; 775,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 174,68</t>
+          <t>-19,89; 173,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-66,45; 49,83</t>
+          <t>-64,79; 63,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212,86; 770,91</t>
+          <t>227,87; 756,79</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,17</t>
+          <t>4,28</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>5,62</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>5,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,74</t>
+          <t>-2,12; 2,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,49</t>
+          <t>-0,08; 5,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,23</t>
+          <t>1,55; 7,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 7,17</t>
+          <t>0,35; 7,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 7,57</t>
+          <t>0,06; 7,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 7,02</t>
+          <t>2,61; 8,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 4,07</t>
+          <t>0,02; 4,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,52</t>
+          <t>0,76; 5,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,42</t>
+          <t>2,86; 7,2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>205,92%</t>
+          <t>211,41%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>133,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131,33%</t>
+          <t>160,66%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-71,41; 308,76</t>
+          <t>-69,46; 280,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 538,19</t>
+          <t>-18,52; 471,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,35; 742,72</t>
+          <t>28,38; 719,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,61; 260,12</t>
+          <t>3,15; 233,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 262,29</t>
+          <t>-0,71; 255,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 240,55</t>
+          <t>42,6; 327,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 172,26</t>
+          <t>-2,32; 187,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,81; 245,38</t>
+          <t>15,37; 240,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34,42; 271,05</t>
+          <t>62,97; 327,46</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11,58</t>
+          <t>10,66</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,05</t>
+          <t>16,09</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>13,55</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,46</t>
+          <t>2,45; 10,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 2,04</t>
+          <t>-3,02; 2,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,31; 16,13</t>
+          <t>6,66; 14,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 7,98</t>
+          <t>-1,49; 7,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,62</t>
+          <t>-4,59; 2,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,27; 21,49</t>
+          <t>11,6; 20,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,26</t>
+          <t>1,52; 7,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,59</t>
+          <t>-3,14; 1,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,55; 17,97</t>
+          <t>10,75; 16,73</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>625,31%</t>
+          <t>575,54%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>427,26%</t>
+          <t>403,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>497,76%</t>
+          <t>461,94%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>30,28; 1655,47</t>
+          <t>39,71; 1586,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 401,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>177,34; 2768,49</t>
+          <t>149,98; 2469,41</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 371,23</t>
+          <t>-29,12; 379,75</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-77,17; 135,83</t>
+          <t>-76,59; 126,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>157,17; 1042,52</t>
+          <t>147,65; 981,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,03; 454,74</t>
+          <t>25,71; 418,62</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-65,89; 113,87</t>
+          <t>-72,02; 77,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>233,6; 1018,78</t>
+          <t>222,9; 937,19</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12,08</t>
+          <t>11,81</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,65</t>
+          <t>11,6</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11,82</t>
+          <t>11,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,39; 6,84</t>
+          <t>0,55; 7,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 3,78</t>
+          <t>-1,16; 3,93</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8,56; 15,81</t>
+          <t>8,54; 15,72</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,84</t>
+          <t>-3,64; 3,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 1,07</t>
+          <t>-5,22; 1,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,65; 15,86</t>
+          <t>7,63; 15,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,85</t>
+          <t>-0,64; 3,87</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 1,6</t>
+          <t>-2,24; 1,85</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9,21; 14,53</t>
+          <t>8,94; 14,28</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>655,59%</t>
+          <t>641,0%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>274,42%</t>
+          <t>273,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>386,41%</t>
+          <t>381,52%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 942,89</t>
+          <t>-0,86; 959,63</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-47,94; 577,23</t>
+          <t>-47,79; 575,47</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>224,05; 1963,64</t>
+          <t>192,72; 1845,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-60,65; 113,74</t>
+          <t>-59,89; 146,35</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-84,07; 56,95</t>
+          <t>-83,12; 67,09</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>104,0; 629,06</t>
+          <t>111,43; 619,65</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 178,7</t>
+          <t>-20,52; 205,24</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-57,0; 74,2</t>
+          <t>-55,4; 93,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>206,34; 737,44</t>
+          <t>195,85; 720,23</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>2,74</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,29</t>
+          <t>3,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 2,5</t>
+          <t>-1,67; 2,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 3,21</t>
+          <t>-1,33; 2,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,91</t>
+          <t>0,4; 4,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,05</t>
+          <t>-1,72; 3,02</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 2,7</t>
+          <t>-2,04; 2,58</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 4,88</t>
+          <t>1,84; 6,68</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,04</t>
+          <t>-1,13; 2,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,2</t>
+          <t>-1,01; 2,06</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,15</t>
+          <t>1,93; 5,15</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 135,79</t>
+          <t>-41,97; 117,33</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-35,79; 163,39</t>
+          <t>-34,5; 133,63</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1,43; 223,05</t>
+          <t>6,28; 225,07</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 94,32</t>
+          <t>-30,72; 84,45</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 77,18</t>
+          <t>-35,27; 70,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-42,13; 127,54</t>
+          <t>26,8; 190,79</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 66,52</t>
+          <t>-23,38; 70,91</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,97; 69,01</t>
+          <t>-22,31; 67,11</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 126,04</t>
+          <t>40,3; 167,07</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,66</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,44</t>
+          <t>-2,33; 1,3</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,57</t>
+          <t>-2,06; 1,49</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,56</t>
+          <t>-1,09; 2,23</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 3,59</t>
+          <t>-0,01; 3,51</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,65</t>
+          <t>-0,56; 2,82</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,14</t>
+          <t>-0,72; 2,17</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,11</t>
+          <t>-0,51; 2,06</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,72</t>
+          <t>-0,89; 1,69</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,47</t>
+          <t>-0,51; 1,8</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-10,02%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-56,69; 69,13</t>
+          <t>-58,2; 58,39</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-52,78; 75,81</t>
+          <t>-53,68; 74,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-68,62; 63,44</t>
+          <t>-30,53; 103,75</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 250,42</t>
+          <t>-1,37; 228,42</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-26,97; 171,59</t>
+          <t>-20,48; 184,07</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 144,96</t>
+          <t>-23,06; 143,02</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 110,2</t>
+          <t>-17,11; 98,16</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-26,72; 79,12</t>
+          <t>-28,66; 86,79</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-34,94; 67,62</t>
+          <t>-14,72; 93,32</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,24</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>4,21</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,4</t>
+          <t>0,56; 2,32</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,15</t>
+          <t>-0,56; 1,09</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,4</t>
+          <t>2,66; 4,57</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,79</t>
+          <t>0,73; 2,76</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,48</t>
+          <t>-0,54; 1,36</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,29</t>
+          <t>3,83; 5,61</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,36</t>
+          <t>0,93; 2,31</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,99</t>
+          <t>-0,25; 0,99</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,59</t>
+          <t>3,53; 4,86</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>127,61%</t>
+          <t>136,02%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>117,89%</t>
+          <t>133,06%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>122,29%</t>
+          <t>134,71%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>14,96; 110,7</t>
+          <t>18,95; 101,56</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 52,04</t>
+          <t>-18,65; 47,66</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>61,79; 199,35</t>
+          <t>85,67; 201,42</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>17,18; 89,73</t>
+          <t>16,06; 87,5</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 47,18</t>
+          <t>-13,82; 42,96</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>73,61; 169,91</t>
+          <t>93,52; 180,65</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>28,91; 83,67</t>
+          <t>26,45; 81,36</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 34,88</t>
+          <t>-7,89; 34,46</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>84,02; 158,33</t>
+          <t>103,95; 172,45</t>
         </is>
       </c>
     </row>
